--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487585_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487585_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3101</v>
+        <v>2.1104</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1675</v>
+        <v>0.333</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4776</v>
+        <v>1.7774</v>
       </c>
       <c r="G2" t="n">
         <v>0.7809</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2066</v>
+        <v>-0.4063</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6057</v>
+        <v>-0.1052</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6009</v>
+        <v>-0.3011</v>
       </c>
       <c r="V2" t="n">
         <v>0.3776</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>A. OLMEDO VELASCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6762</v>
+        <v>0.9629</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.9783</v>
+        <v>-1.6502</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6545</v>
+        <v>2.6132</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6137</v>
+        <v>0.2245</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.4016</v>
+        <v>-0.8544</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7879</v>
+        <v>1.0789</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.3664</v>
+        <v>-0.1657</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5694</v>
+        <v>0.4738</v>
       </c>
       <c r="L3" t="n">
-        <v>0.203</v>
+        <v>-0.6395</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7527</v>
+        <v>0.3902</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8321</v>
+        <v>-1.3281</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5849</v>
+        <v>1.7183</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5821</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9105</v>
+        <v>-4.8508</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4926</v>
+        <v>4.2687</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6496</v>
+        <v>-0.1004</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0165</v>
+        <v>0.3544</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3669</v>
+        <v>-0.4547</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9418</v>
+        <v>1.4209</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>3.0119</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2239</v>
+        <v>-1.591</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. FINI</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6239</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2197</v>
+        <v>0.4006</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5958</v>
+        <v>0.4416</v>
       </c>
       <c r="G4" t="n">
-        <v>1.305</v>
+        <v>1.8678</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0381</v>
+        <v>-0.7827</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2669</v>
+        <v>2.6505</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9886</v>
+        <v>1.5187</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9886</v>
+        <v>-0.8815</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.4002</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3164</v>
+        <v>0.3491</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0494</v>
+        <v>0.0989</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2669</v>
+        <v>0.2502</v>
       </c>
       <c r="P4" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6308</v>
+        <v>-0.7733</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4251</v>
+        <v>-0.0718</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2057</v>
+        <v>-0.7015</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.506</v>
+        <v>0.3299</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.506</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. OLMEDO VELASCO</t>
+          <t>I. FINI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1961</v>
+        <v>0.3781</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1718</v>
+        <v>0.9194</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3679</v>
+        <v>-0.5413</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2245</v>
+        <v>1.305</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8544</v>
+        <v>1.0381</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0789</v>
+        <v>0.2669</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1657</v>
+        <v>0.9886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4738</v>
+        <v>0.9886</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6395</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3902</v>
+        <v>0.3164</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3281</v>
+        <v>0.0494</v>
       </c>
       <c r="O5" t="n">
-        <v>1.7183</v>
+        <v>0.2669</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8508</v>
+        <v>-0.194</v>
       </c>
       <c r="R5" t="n">
-        <v>4.2687</v>
+        <v>0.3881</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8672</v>
+        <v>0.385</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1672</v>
+        <v>0.1248</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7</v>
+        <v>0.2602</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4209</v>
+        <v>-1.506</v>
       </c>
       <c r="W5" t="n">
-        <v>3.0119</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.591</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.142</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002</v>
+        <v>-2.1168</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1418</v>
+        <v>2.1823</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8678</v>
+        <v>0.5242</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7827</v>
+        <v>0.3501</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6505</v>
+        <v>0.1741</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5187</v>
+        <v>-0.8368</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8815</v>
+        <v>0.4573</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4002</v>
+        <v>-1.2941</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3491</v>
+        <v>1.361</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0989</v>
+        <v>-0.1071</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2502</v>
+        <v>1.4681</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4735</v>
+        <v>0.3668</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4722</v>
+        <v>0.2619</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0013</v>
+        <v>0.1049</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3299</v>
+        <v>-1.6015</v>
       </c>
       <c r="W6" t="n">
-        <v>0.894</v>
+        <v>-0.3776</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3799</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.317</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9371</v>
+        <v>-0.643</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5242</v>
+        <v>1.8359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3501</v>
+        <v>1.5868</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1741</v>
+        <v>0.2492</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8368</v>
+        <v>1.2757</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4573</v>
+        <v>1.9608</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2941</v>
+        <v>-0.6851</v>
       </c>
       <c r="M7" t="n">
-        <v>1.361</v>
+        <v>0.5602</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1071</v>
+        <v>-0.374</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4681</v>
+        <v>0.9343</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.5821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0617</v>
+        <v>0.5226</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1404</v>
+        <v>0.0595</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6015</v>
+        <v>-1.9209</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3776</v>
+        <v>0.894</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-2.8149</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6566</v>
+        <v>-0.502</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.73</v>
+        <v>-0.6299</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1279</v>
       </c>
       <c r="G8" t="n">
         <v>0.0832</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1577</v>
+        <v>-0.0031</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0606</v>
+        <v>0.0395</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8245</v>
+        <v>-0.5674</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0365</v>
+        <v>-3.0584</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.861</v>
+        <v>2.491</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8359</v>
+        <v>-0.6137</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5868</v>
+        <v>-2.4016</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2492</v>
+        <v>1.7879</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2757</v>
+        <v>-1.3664</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9608</v>
+        <v>-1.5694</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6851</v>
+        <v>0.203</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5602</v>
+        <v>0.7527</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.374</v>
+        <v>-0.8321</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9343</v>
+        <v>1.5849</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5821</v>
+        <v>0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1344</v>
+        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5523</v>
+        <v>3.4926</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1575</v>
+        <v>0.406</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0011</v>
+        <v>0.9365</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1586</v>
+        <v>-0.5305</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9209</v>
+        <v>-0.9418</v>
       </c>
       <c r="W9" t="n">
-        <v>0.894</v>
+        <v>0.2821</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8149</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2465</v>
+        <v>-2.0861</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2573</v>
+        <v>-2.1667</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0108</v>
+        <v>0.0806</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9385</v>
+        <v>0.7944</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.469</v>
+        <v>1.6642</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4074</v>
+        <v>-0.8698</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1081</v>
+        <v>0.7733</v>
       </c>
       <c r="K10" t="n">
-        <v>0.103</v>
+        <v>1.3594</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005</v>
+        <v>-0.5861</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8304</v>
+        <v>0.0212</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.572</v>
+        <v>0.3048</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4024</v>
+        <v>-0.2836</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1344</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0448</v>
+        <v>-2.9105</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9105</v>
+        <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0673</v>
+        <v>-0.0193</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3974</v>
+        <v>-0.3115</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.2922</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1179</v>
+        <v>-1.309</v>
       </c>
       <c r="W10" t="n">
         <v>0.2821</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4</v>
+        <v>-1.591</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2868</v>
+        <v>-2.1437</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2668</v>
+        <v>-3.6366</v>
       </c>
       <c r="F11" t="n">
-        <v>0.98</v>
+        <v>1.4929</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7944</v>
+        <v>0.9385</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6642</v>
+        <v>-1.469</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8698</v>
+        <v>2.4074</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7733</v>
+        <v>0.1081</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3594</v>
+        <v>0.103</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5861</v>
+        <v>0.005</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0212</v>
+        <v>0.8304</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3048</v>
+        <v>-1.572</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2836</v>
+        <v>2.4024</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5523</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9105</v>
+        <v>-5.0448</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3582</v>
+        <v>2.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.78</v>
+        <v>1.1701</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4116</v>
+        <v>1.0181</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1916</v>
+        <v>0.152</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.309</v>
+        <v>-2.1179</v>
       </c>
       <c r="W11" t="n">
         <v>0.2821</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.591</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3551</v>
+        <v>-2.604</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6328</v>
+        <v>-0.0518</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2776</v>
+        <v>-2.5521</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0134</v>
+        <v>-1.3578</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9237</v>
+        <v>-2.4889</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9104</v>
+        <v>1.1311</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9922</v>
+        <v>-0.8881</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6189</v>
+        <v>-0.9516</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6267</v>
+        <v>0.0634</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0212</v>
+        <v>-0.4696</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3048</v>
+        <v>-1.5374</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2836</v>
+        <v>1.0677</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.7164</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8806</v>
+        <v>-2.1344</v>
       </c>
       <c r="R12" t="n">
         <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2849</v>
+        <v>0.0911</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2557</v>
+        <v>0.2408</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5406</v>
+        <v>-0.1497</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3672</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3672</v>
+        <v>-3.097</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0526</v>
+        <v>-2.6193</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4733</v>
+        <v>-3.0332</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5794</v>
+        <v>0.4139</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3578</v>
+        <v>1.0134</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4889</v>
+        <v>1.9237</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1311</v>
+        <v>-0.9104</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8881</v>
+        <v>0.9922</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9516</v>
+        <v>1.6189</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0634</v>
+        <v>-0.6267</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4696</v>
+        <v>0.0212</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5374</v>
+        <v>0.3048</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0677</v>
+        <v>-0.2836</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9702</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1344</v>
+        <v>-3.8806</v>
       </c>
       <c r="R13" t="n">
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3576</v>
+        <v>-0.549</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1806</v>
+        <v>-0.1447</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.177</v>
+        <v>-0.4043</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3672</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.097</v>
+        <v>-0.3672</v>
       </c>
     </row>
     <row r="14">
@@ -1501,37 +1501,37 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.8537</v>
+        <v>-6.2483</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.7384</v>
+        <v>-14.1326</v>
       </c>
       <c r="F14" t="n">
-        <v>7.884500000000001</v>
+        <v>7.884400000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>7.396300000000001</v>
+        <v>7.396299999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.334900000000001</v>
+        <v>-1.3349</v>
       </c>
       <c r="I14" t="n">
         <v>8.731000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1385</v>
+        <v>3.138499999999999</v>
       </c>
       <c r="K14" t="n">
         <v>5.001</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8628</v>
+        <v>-1.862800000000001</v>
       </c>
       <c r="M14" t="n">
         <v>4.258000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.335699999999999</v>
+        <v>-6.3357</v>
       </c>
       <c r="O14" t="n">
         <v>10.5937</v>
@@ -1546,16 +1546,16 @@
         <v>21.3436</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5440000000000003</v>
+        <v>1.1497</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2596</v>
+        <v>2.8654</v>
       </c>
       <c r="U14" t="n">
         <v>-1.7156</v>
       </c>
       <c r="V14" t="n">
-        <v>-8.0031</v>
+        <v>-8.003100000000002</v>
       </c>
       <c r="W14" t="n">
         <v>7.998399999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5355</v>
+        <v>7.2912</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4813</v>
+        <v>4.4823</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0542</v>
+        <v>2.8089</v>
       </c>
       <c r="G15" t="n">
         <v>1.4767</v>
@@ -1624,13 +1624,13 @@
         <v>3.8806</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5352</v>
+        <v>-0.7795</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5747</v>
+        <v>-0.5737</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0395</v>
+        <v>-0.2058</v>
       </c>
       <c r="V15" t="n">
         <v>4.8477</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9072</v>
+        <v>3.8856</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9955</v>
+        <v>3.7746</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7952</v>
@@ -1702,13 +1702,13 @@
         <v>4.8508</v>
       </c>
       <c r="S16" t="n">
-        <v>2.201</v>
+        <v>1.1793</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6644</v>
+        <v>0.8636</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5366</v>
+        <v>0.3158</v>
       </c>
       <c r="V16" t="n">
         <v>3.5015</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.317</v>
+        <v>3.2219</v>
       </c>
       <c r="E17" t="n">
-        <v>1.83</v>
+        <v>-0.5605</v>
       </c>
       <c r="F17" t="n">
-        <v>0.487</v>
+        <v>3.7824</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9384</v>
+        <v>-0.2298</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2688</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3303</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2909</v>
+        <v>-0.3554</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6591</v>
+        <v>-0.4366</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6318</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3525</v>
+        <v>0.1256</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6096</v>
+        <v>-0.5306</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9621</v>
+        <v>0.6562</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.0747</v>
+        <v>-2.1344</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9105</v>
+        <v>3.6866</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8995</v>
+        <v>0.798</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1078</v>
+        <v>0.7054</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2083</v>
+        <v>0.0926</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3567</v>
+        <v>1.1015</v>
       </c>
       <c r="W17" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8626</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9333</v>
+        <v>0.944</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3613</v>
+        <v>-3.2864</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2946</v>
+        <v>4.2304</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2298</v>
+        <v>-1.8511</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.5085</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.3426</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3554</v>
+        <v>-1.664</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4366</v>
+        <v>-0.9433</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.7207</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1256</v>
+        <v>-0.1871</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5306</v>
+        <v>-0.5652</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6562</v>
+        <v>0.3781</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5523</v>
+        <v>2.5224</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6866</v>
+        <v>4.4627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4906</v>
+        <v>-0.6214</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0954</v>
+        <v>-0.2462</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3952</v>
+        <v>-0.3751</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1015</v>
+        <v>0.894</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>0.5642</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1224</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.5397</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4541</v>
+        <v>0.0282</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5492</v>
+        <v>0.5115</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8689</v>
+        <v>0.9384</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0694</v>
+        <v>1.2688</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7995</v>
+        <v>-0.3303</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.6124</v>
+        <v>1.2909</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5571</v>
+        <v>0.6591</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0553</v>
+        <v>0.6318</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7435</v>
+        <v>-0.3525</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4877</v>
+        <v>0.6096</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2558</v>
+        <v>-0.9621</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4.0747</v>
+      </c>
+      <c r="R19" t="n">
         <v>2.9105</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.8806</v>
-      </c>
       <c r="S19" t="n">
-        <v>0.6178</v>
+        <v>1.1221</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0954</v>
+        <v>1.306</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7131</v>
+        <v>-0.1839</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5642</v>
+        <v>-0.3567</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.788</v>
+        <v>-1.8626</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4903</v>
+        <v>0.193</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2874</v>
+        <v>-3.0537</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7971</v>
+        <v>3.2466</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8511</v>
+        <v>-2.8689</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5085</v>
+        <v>-1.0694</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3426</v>
+        <v>-1.7995</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.664</v>
+        <v>-3.6124</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9433</v>
+        <v>-1.5571</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7207</v>
+        <v>-2.0553</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1871</v>
+        <v>0.7435</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5652</v>
+        <v>0.4877</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3781</v>
+        <v>0.2558</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5224</v>
+        <v>2.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>4.4627</v>
+        <v>3.8806</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0556</v>
+        <v>0.7156</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2472</v>
+        <v>0.305</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8084</v>
+        <v>0.4105</v>
       </c>
       <c r="V20" t="n">
-        <v>0.894</v>
+        <v>-0.5642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5642</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3299</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5947</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8956</v>
+        <v>-0.9371</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3009</v>
+        <v>-0.0543</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.339</v>
+        <v>-1.1102</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4614</v>
+        <v>-1.946</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1223</v>
+        <v>0.8358</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8816000000000001</v>
+        <v>-0.429</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8816000000000001</v>
+        <v>-0.4696</v>
       </c>
       <c r="L21" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.6812</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.4764</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.7952</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.5523</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="n">
-        <v>-1.2206</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-1.3429</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.1223</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-1.1642</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-3.1045</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3712</v>
+        <v>-0.8216</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0453</v>
+        <v>-0.5081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.674</v>
+        <v>-0.3135</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5373</v>
+        <v>-0.6119</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.2552</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5826</v>
+        <v>-1.4594</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3375</v>
+        <v>-1.8966</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2451</v>
+        <v>0.4372</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1102</v>
+        <v>-0.339</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.946</v>
+        <v>-0.4614</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8358</v>
+        <v>0.1223</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.429</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4696</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6812</v>
+        <v>-1.2206</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4764</v>
+        <v>-1.3429</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7952</v>
+        <v>0.1223</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5523</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4127</v>
+        <v>-0.4935</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9085</v>
+        <v>0.0443</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5042</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6119</v>
+        <v>0.5373</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6119</v>
+        <v>0.2552</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.267</v>
+        <v>-6.1035</v>
       </c>
       <c r="E23" t="n">
         <v>-2.7717</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4952</v>
+        <v>-3.3317</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6172</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1393</v>
+        <v>-0.9758</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1806</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9587</v>
+        <v>-0.7952</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3463</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.853599999999997</v>
+        <v>7.521100000000001</v>
       </c>
       <c r="E24" t="n">
         <v>-7.8845</v>
       </c>
       <c r="F24" t="n">
-        <v>14.7382</v>
+        <v>15.4056</v>
       </c>
       <c r="G24" t="n">
         <v>-7.3963</v>
@@ -2299,7 +2299,7 @@
         <v>-8.731</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.257899999999999</v>
+        <v>-4.2579</v>
       </c>
       <c r="K24" t="n">
         <v>6.3357</v>
@@ -2326,13 +2326,13 @@
         <v>28.1346</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5439000000000003</v>
+        <v>0.1232000000000002</v>
       </c>
       <c r="T24" t="n">
         <v>1.7157</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.2596</v>
+        <v>-1.5924</v>
       </c>
       <c r="V24" t="n">
         <v>8.0029</v>
@@ -2341,7 +2341,7 @@
         <v>16.0015</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.998200000000001</v>
+        <v>-7.9982</v>
       </c>
     </row>
   </sheetData>
